--- a/WorkBot/main/data/order_archive/Sysco/Sysco_Bakery_20260726.xlsx
+++ b/WorkBot/main/data/order_archive/Sysco/Sysco_Bakery_20260726.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1130,6 +1130,90 @@
         <v>69.89</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>7119250</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Naked - Mighty Mango</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>26.89</v>
+      </c>
+      <c r="E37" t="n">
+        <v>53.78</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>7119269</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Naked - Green Machine</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>26.89</v>
+      </c>
+      <c r="E38" t="n">
+        <v>53.78</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>7119223</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Naked - Strawberry Banana</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>26.89</v>
+      </c>
+      <c r="E39" t="n">
+        <v>53.78</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>7119284</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Naked - Blue Machine</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>26.89</v>
+      </c>
+      <c r="E40" t="n">
+        <v>53.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
